--- a/店家數據/整骨&公園/公園/全台寵物公園.xlsx
+++ b/店家數據/整骨&公園/公園/全台寵物公園.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonnie\Desktop\整骨&amp;公園\公園\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F193A113-C45A-4115-B680-24120B635642}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11E264F-CCD6-4715-A34D-8734994FFE71}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6880" xr2:uid="{9283FED0-5499-4093-8822-C7CEED6C1D9C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="公園" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">公園!$A$1:$D$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">公園!$A$1:$D$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1524,7 +1524,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C3CE7E-7D8C-44D7-9116-3BF1DF3826E2}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
@@ -1547,7 +1546,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1562,7 +1561,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1577,7 +1576,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -1592,7 +1591,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1607,7 +1606,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
@@ -1622,7 +1621,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -1637,7 +1636,7 @@
         <v>高雄市</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -1652,7 +1651,7 @@
         <v>高雄市</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
@@ -1667,7 +1666,7 @@
         <v>高雄市</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
@@ -1682,7 +1681,7 @@
         <v>高雄市</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1">
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -1712,7 +1711,7 @@
         <v>台北市</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1">
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1727,7 +1726,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1">
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -1742,7 +1741,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1">
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -1757,7 +1756,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
@@ -1772,7 +1771,7 @@
         <v>台中市</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1">
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -1787,7 +1786,7 @@
         <v>新竹市</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1">
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -1802,7 +1801,7 @@
         <v>新竹市</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1">
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>49</v>
       </c>
@@ -1817,7 +1816,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1">
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
@@ -1832,7 +1831,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1">
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
@@ -1847,7 +1846,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1">
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>50</v>
       </c>
@@ -1862,7 +1861,7 @@
         <v>台中市</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1">
+    <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
         <v>51</v>
       </c>
@@ -1877,7 +1876,7 @@
         <v>台中市</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1">
+    <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
@@ -1892,7 +1891,7 @@
         <v>台中市</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1">
+    <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -1907,7 +1906,7 @@
         <v>新竹縣</v>
       </c>
     </row>
-    <row r="26" spans="1:4" hidden="1">
+    <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
@@ -1937,7 +1936,7 @@
         <v>台北市</v>
       </c>
     </row>
-    <row r="28" spans="1:4" hidden="1">
+    <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -1952,7 +1951,7 @@
         <v>台中市</v>
       </c>
     </row>
-    <row r="29" spans="1:4" hidden="1">
+    <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
@@ -2042,7 +2041,7 @@
         <v>台北市</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1">
+    <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
         <v>17</v>
       </c>
@@ -2057,7 +2056,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1">
+    <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
         <v>52</v>
       </c>
@@ -2072,7 +2071,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1">
+    <row r="37" spans="1:4">
       <c r="A37" s="4" t="s">
         <v>58</v>
       </c>
@@ -2087,7 +2086,7 @@
         <v>苗栗縣</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1">
+    <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
         <v>59</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>彰化縣</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1">
+    <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
         <v>60</v>
       </c>
@@ -2117,7 +2116,7 @@
         <v>台南市</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="34" hidden="1">
+    <row r="40" spans="1:4" ht="34">
       <c r="A40" s="3" t="s">
         <v>61</v>
       </c>
@@ -2327,7 +2326,7 @@
         <v>台北市</v>
       </c>
     </row>
-    <row r="54" spans="1:4" hidden="1">
+    <row r="54" spans="1:4">
       <c r="A54" s="4" t="s">
         <v>36</v>
       </c>
@@ -2342,7 +2341,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="55" spans="1:4" hidden="1">
+    <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
         <v>66</v>
       </c>
@@ -2357,7 +2356,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="56" spans="1:4" hidden="1">
+    <row r="56" spans="1:4">
       <c r="A56" s="4" t="s">
         <v>30</v>
       </c>
@@ -2372,7 +2371,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="57" spans="1:4" hidden="1">
+    <row r="57" spans="1:4">
       <c r="A57" s="4" t="s">
         <v>37</v>
       </c>
@@ -2387,7 +2386,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="58" spans="1:4" hidden="1">
+    <row r="58" spans="1:4">
       <c r="A58" s="4" t="s">
         <v>68</v>
       </c>
@@ -2402,7 +2401,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1">
+    <row r="59" spans="1:4">
       <c r="A59" s="4" t="s">
         <v>69</v>
       </c>
@@ -2417,7 +2416,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="60" spans="1:4" hidden="1">
+    <row r="60" spans="1:4">
       <c r="A60" s="4" t="s">
         <v>70</v>
       </c>
@@ -2432,7 +2431,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="61" spans="1:4" hidden="1">
+    <row r="61" spans="1:4">
       <c r="A61" s="2" t="s">
         <v>5</v>
       </c>
@@ -2447,7 +2446,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -2462,7 +2461,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="63" spans="1:4" hidden="1">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -2477,7 +2476,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>26</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>新北市</v>
       </c>
     </row>
-    <row r="65" spans="1:4" hidden="1">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>28</v>
       </c>
@@ -2507,7 +2506,7 @@
         <v>桃園市</v>
       </c>
     </row>
-    <row r="66" spans="1:4" hidden="1">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>31</v>
       </c>
@@ -2538,13 +2537,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D66" xr:uid="{5747D1EB-3E44-4FD5-BC3E-01A309D52300}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="台北市"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D67" xr:uid="{5747D1EB-3E44-4FD5-BC3E-01A309D52300}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
